--- a/[Work]/Work_YX/9_11_Task1/中国氢能网/2025_News/logs/news_log.xlsx
+++ b/[Work]/Work_YX/9_11_Task1/中国氢能网/2025_News/logs/news_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2070,6 +2070,286 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>44b3584774a1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>打造全链条绿色消纳体系 绿氨“零碳工厂”让新能源“就地生金”</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233810.html</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233810</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>37237</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2025-09-16 11:01:31</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>bafec3d838d5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>儋州：加速壮大氢能产业，探索“制、储、运、用”产业链发展</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233804.html</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>39897</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2025-09-16 11:01:32</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>67242266ee38</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>年内力争新增1000辆氢能重卡！《孝义市实施燃料电池汽车示范应用推广 推动空气质量持续改善行动方案》印发</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233834.html</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>40753</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2025-09-16 16:44:02</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1eee77f5c40f</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>从“三零”绿色焊接到氢能全产业链：记者团探访德阳绿色智造现场</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233833.html</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233833</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>37229</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2025-09-16 16:44:03</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>b8f9d1b58ce2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>《氢气（含液氢）道路运输技术规范》发布</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233832.html</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>37477</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2025-09-16 16:44:04</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>27a850ca4f29</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>交通运输部：推进甲醇、氢燃料电池等船舶建造及使用</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233831.html</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>38103</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2025-09-16 16:44:06</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>c21011907fc6</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>超过500个清洁氢项目，总投资高达1100亿美元，中国位居全球首位</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233829.html</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233829</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>37221</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2025-09-16 16:44:07</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/[Work]/Work_YX/9_11_Task1/中国氢能网/2025_News/logs/news_log.xlsx
+++ b/[Work]/Work_YX/9_11_Task1/中国氢能网/2025_News/logs/news_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2350,6 +2350,966 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8fa3b9bdb010</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>氢蓝时代联袂华南造船厂共同打造氢燃料电池动力船舶示范项目</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234083.html</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>38701</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:26</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>748fc1dab76a</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>慕帆动力全球首台氢氨双燃料燃气轮机机组总装下线</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234082.html</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>37550</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:27</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>c61f3397315b</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>科环集团烟台龙源掺氢燃烧团队成功完成氢气点火试验</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234081.html</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>37796</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:29</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>019e3ce4c43b</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>国资委公布央企11个氢能中试平台项目</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234080.html</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>47359</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:30</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ab9a21fcd554</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>最高补贴2000万元，成都开展加氢基础设施建设、氢能应用场景打造奖励项目申报工作</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234079.html</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>37144</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:32</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>24292f21b28b</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>氢能共享单车上路！补能1分钟续航可达100公里</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234077.html</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=234077</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>37234</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:33</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>c3a81fd87a23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>氢能产业逐渐走到深水区 北京以标准助力产业破局</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234076.html</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=234076</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>37184</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:35</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3213642eb685</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>“山西建造”竞逐绿醇新赛道</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234048.html</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=234048</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>37221</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:37</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6c33f019ef68</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>联合能源：连签毛里塔尼亚、约旦两大绿氢项目</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234047.html</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>37820</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:38</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>e5f1f3a63a18</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>国际首创、可规模化应用！风光发电离网制氢直流微网供电系统联调成功</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234045.html</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>39041</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:39</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>05dfad3c42c4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>嘉定氢能港：打造氢能应用新范式，助力能源产业新征程</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/234043.html</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=234043</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>37219</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:41</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>a0d6870b943e</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>兴邦能源首批氢能两轮车顺利交付北京理工大学</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233994.html</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>37803</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:43</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3ee703bb3153</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>《氢能汽车蓝皮书：中国车用氢能产业发展报告 (2024)》发布</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233992.html</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233992</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>37158</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:44</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2987892752c5</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>北京银行大兴国际氢能示范区支行开业</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233991.html</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>37871</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:45</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>178bd1f2e083</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>国内首台全自主纯氢重型燃机在德阳发布</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233990.html</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233990</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>37190</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:46</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3f51dd5bfc49</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>300辆！北京启动2025年度北京市燃料电池汽车示范应用项目申报</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233989.html</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>39420</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:48</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>b9d50420c0c5</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>绿色交通新地标！德阳首座制氢加氢一体站投用</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233988.html</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233988</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>37179</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:50</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>06c075d82c2f</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>承德市清洁能源电力总装机达2397.5万千瓦</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233987.html</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233987</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>37219</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:51</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4a5b2493457b</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>国华投资（氢能公司）获国家能源集团首张国际绿氨碳足迹预评价证书</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233971.html</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>37964</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>54380fa89eaf</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>中来股份与ACWA Power共探可再生能源制绿氢</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233969.html</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>38178</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:54</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cf2f73f6a2f7</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>埃及加速布局绿氢产业</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233967.html</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233967</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>37204</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:55</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>b27439e48e32</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>中船科技签与客户签订绿色甲醇销售合同，每年最高8.5亿元</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233966.html</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>37268</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:57</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>5c80b976d5c3</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>华电河北新能源“零碳示范园区”</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233965.html</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233965</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>37192</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:58</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>d4767bf4e845</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>阳江希倍优氢能首台集装箱式制氢系统下线</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/news/233964.html</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>http://h2.china-nengyuan.com/elink/?news_id=233964</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>37190</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2025-09-19 16:33:59</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
